--- a/examples/excel/charts/charts-bubble.xlsx
+++ b/examples/excel/charts/charts-bubble.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-Bubble Fundamentals" sheetId="2" r:id="R94e6de2e405548c0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-Bubble Styling" sheetId="3" r:id="R8651c580bff448c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-Bubble Advanced" sheetId="4" r:id="Rb772f0f24c0946ad"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4-Bubble Series Data" sheetId="5" r:id="R20defc9ada9347a5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1-Bubble Fundamentals" sheetId="2" r:id="Rab1c6d59164f4f3e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2-Bubble Styling" sheetId="3" r:id="R8b8ac7b6753742f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-Bubble Advanced" sheetId="4" r:id="Redcea6eff7c94ee1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4-Bubble Series Data" sheetId="5" r:id="R10cb62ea0cb44d08"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2517,7 +2517,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8669af0058894249"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1b8db0e5a8554ccb"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2547,7 +2547,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R82e24ef50bed4ff6"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rea5b882513064e8c"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2577,7 +2577,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rb2f6c0ff13df473b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf4dcce745a08442f"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2607,7 +2607,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R7a9a0edcdb294a46"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re7b8593a4e7d4463"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2642,7 +2642,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra515e3a58ea643f2"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R975c64eeefbe469a"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2672,7 +2672,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R00177e7c834e4528"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5822a5ba936d4d28"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2702,7 +2702,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf219012cd51443a5"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4cfb311ac80b4a44"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2732,7 +2732,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8609542f62824a8b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R89a2b15c3a9543cd"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2767,7 +2767,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rf7ec639841f0497b"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra1fedff1fea94a87"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2797,7 +2797,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R629be0847cf1462e"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R4493050440524630"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2827,7 +2827,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc3bf729d323944a7"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R9af5a3fac3e84239"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2857,7 +2857,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5fdc2e203a794012"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R69d637c8f56f4497"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2892,7 +2892,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6b78d3b8e6be4037"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R5fdd4a89a37d49c7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2922,7 +2922,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R285cba787bb1454f"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Ra2cd85c67c5744b7"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2931,24 +2931,133 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="12700" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+        <a:ln w="19050" cap="flat">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rdf035b1de3824a23"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1ef26d2cafdc4b3d"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Raa5d5d48f1544356"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0feaf63720274e90"/>
 </x:worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetData/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re488b6e47efd4ece"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb3736d9f77ed41ad"/>
 </x:worksheet>
 </file>
 
@@ -2971,6 +3080,6 @@
       </x:c>
     </x:row>
   </x:sheetData>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R7bdf3409c82245c1"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R389c45f7d3b3456a"/>
 </x:worksheet>
 </file>